--- a/北京中心顾问薪酬绩效台账_v2.xlsx
+++ b/北京中心顾问薪酬绩效台账_v2.xlsx
@@ -31051,34 +31051,80 @@
       <c r="AT50" s="51" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="51" t="n"/>
-      <c r="B51" s="51" t="n"/>
-      <c r="C51" s="51" t="n"/>
-      <c r="D51" s="51" t="n"/>
-      <c r="E51" s="51" t="n"/>
-      <c r="F51" s="51" t="n"/>
-      <c r="G51" s="51" t="n"/>
-      <c r="H51" s="51" t="n"/>
-      <c r="I51" s="51" t="n"/>
-      <c r="J51" s="51" t="n"/>
-      <c r="K51" s="51" t="n"/>
-      <c r="L51" s="51" t="n"/>
-      <c r="M51" s="51" t="n"/>
-      <c r="N51" s="51" t="n"/>
-      <c r="O51" s="51" t="n"/>
-      <c r="P51" s="51" t="n"/>
-      <c r="Q51" s="51" t="n"/>
-      <c r="R51" s="51" t="n"/>
-      <c r="S51" s="51" t="n"/>
-      <c r="T51" s="51" t="n"/>
-      <c r="U51" s="51" t="n"/>
-      <c r="V51" s="51" t="n"/>
-      <c r="W51" s="51" t="n"/>
-      <c r="X51" s="51" t="n"/>
-      <c r="Y51" s="51" t="n"/>
-      <c r="Z51" s="51" t="n"/>
-      <c r="AA51" s="51" t="n"/>
-      <c r="AB51" s="51" t="n"/>
+      <c r="A51" s="53" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B51" s="54" t="inlineStr">
+        <is>
+          <t>刘晓娟</t>
+        </is>
+      </c>
+      <c r="C51" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D51" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E51" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F51" s="55">
+        <f>G51+H51+I51</f>
+        <v/>
+      </c>
+      <c r="G51" s="55">
+        <f>Q51+R51</f>
+        <v/>
+      </c>
+      <c r="H51" s="55">
+        <f>U51-V51</f>
+        <v/>
+      </c>
+      <c r="I51" s="55">
+        <f>AB51</f>
+        <v/>
+      </c>
+      <c r="J51" s="55" t="n">
+        <v>283600</v>
+      </c>
+      <c r="K51" s="55" t="n">
+        <v>558802.25</v>
+      </c>
+      <c r="L51" s="55" t="n">
+        <v>76184.3</v>
+      </c>
+      <c r="M51" s="55" t="n">
+        <v>482617.95</v>
+      </c>
+      <c r="N51" s="56" t="n">
+        <v>1.7017558180536</v>
+      </c>
+      <c r="O51" s="55" t="n"/>
+      <c r="P51" s="56" t="n"/>
+      <c r="Q51" s="55" t="n">
+        <v>24218.5</v>
+      </c>
+      <c r="R51" s="55" t="n"/>
+      <c r="S51" s="55" t="n"/>
+      <c r="T51" s="56" t="n"/>
+      <c r="U51" s="55" t="n">
+        <v>1588.5</v>
+      </c>
+      <c r="V51" s="55" t="n"/>
+      <c r="W51" s="55" t="n"/>
+      <c r="X51" s="55" t="n"/>
+      <c r="Y51" s="55" t="n"/>
+      <c r="Z51" s="55" t="n"/>
+      <c r="AA51" s="56" t="n"/>
+      <c r="AB51" s="55" t="n">
+        <v>2000</v>
+      </c>
       <c r="AC51" s="51" t="n"/>
       <c r="AD51" s="51" t="n"/>
       <c r="AE51" s="51" t="n"/>
@@ -31099,34 +31145,78 @@
       <c r="AT51" s="51" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="51" t="n"/>
-      <c r="B52" s="51" t="n"/>
-      <c r="C52" s="51" t="n"/>
-      <c r="D52" s="51" t="n"/>
-      <c r="E52" s="51" t="n"/>
-      <c r="F52" s="51" t="n"/>
-      <c r="G52" s="51" t="n"/>
-      <c r="H52" s="51" t="n"/>
-      <c r="I52" s="51" t="n"/>
-      <c r="J52" s="51" t="n"/>
-      <c r="K52" s="51" t="n"/>
-      <c r="L52" s="51" t="n"/>
-      <c r="M52" s="51" t="n"/>
-      <c r="N52" s="51" t="n"/>
-      <c r="O52" s="51" t="n"/>
-      <c r="P52" s="51" t="n"/>
-      <c r="Q52" s="51" t="n"/>
-      <c r="R52" s="51" t="n"/>
-      <c r="S52" s="51" t="n"/>
-      <c r="T52" s="51" t="n"/>
-      <c r="U52" s="51" t="n"/>
-      <c r="V52" s="51" t="n"/>
-      <c r="W52" s="51" t="n"/>
-      <c r="X52" s="51" t="n"/>
-      <c r="Y52" s="51" t="n"/>
-      <c r="Z52" s="51" t="n"/>
-      <c r="AA52" s="51" t="n"/>
-      <c r="AB52" s="51" t="n"/>
+      <c r="A52" s="53" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B52" s="54" t="inlineStr">
+        <is>
+          <t>房国超</t>
+        </is>
+      </c>
+      <c r="C52" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D52" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E52" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F52" s="55">
+        <f>G52+H52+I52</f>
+        <v/>
+      </c>
+      <c r="G52" s="55">
+        <f>Q52+R52</f>
+        <v/>
+      </c>
+      <c r="H52" s="55">
+        <f>U52-V52</f>
+        <v/>
+      </c>
+      <c r="I52" s="55">
+        <f>AB52</f>
+        <v/>
+      </c>
+      <c r="J52" s="55" t="n">
+        <v>283600</v>
+      </c>
+      <c r="K52" s="55" t="n">
+        <v>457379.6</v>
+      </c>
+      <c r="L52" s="55" t="n">
+        <v>113972</v>
+      </c>
+      <c r="M52" s="55" t="n">
+        <v>343407.6</v>
+      </c>
+      <c r="N52" s="56" t="n">
+        <v>1.21088716502116</v>
+      </c>
+      <c r="O52" s="55" t="n"/>
+      <c r="P52" s="56" t="n"/>
+      <c r="Q52" s="55" t="n">
+        <v>13924</v>
+      </c>
+      <c r="R52" s="55" t="n"/>
+      <c r="S52" s="55" t="n"/>
+      <c r="T52" s="56" t="n"/>
+      <c r="U52" s="55" t="n"/>
+      <c r="V52" s="55" t="n"/>
+      <c r="W52" s="55" t="n"/>
+      <c r="X52" s="55" t="n"/>
+      <c r="Y52" s="55" t="n"/>
+      <c r="Z52" s="55" t="n"/>
+      <c r="AA52" s="56" t="n"/>
+      <c r="AB52" s="55" t="n">
+        <v>2000</v>
+      </c>
       <c r="AC52" s="51" t="n"/>
       <c r="AD52" s="51" t="n"/>
       <c r="AE52" s="51" t="n"/>
@@ -31147,34 +31237,78 @@
       <c r="AT52" s="51" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="51" t="n"/>
-      <c r="B53" s="51" t="n"/>
-      <c r="C53" s="51" t="n"/>
-      <c r="D53" s="51" t="n"/>
-      <c r="E53" s="51" t="n"/>
-      <c r="F53" s="51" t="n"/>
-      <c r="G53" s="51" t="n"/>
-      <c r="H53" s="51" t="n"/>
-      <c r="I53" s="51" t="n"/>
-      <c r="J53" s="51" t="n"/>
-      <c r="K53" s="51" t="n"/>
-      <c r="L53" s="51" t="n"/>
-      <c r="M53" s="51" t="n"/>
-      <c r="N53" s="51" t="n"/>
-      <c r="O53" s="51" t="n"/>
-      <c r="P53" s="51" t="n"/>
-      <c r="Q53" s="51" t="n"/>
-      <c r="R53" s="51" t="n"/>
-      <c r="S53" s="51" t="n"/>
-      <c r="T53" s="51" t="n"/>
-      <c r="U53" s="51" t="n"/>
-      <c r="V53" s="51" t="n"/>
-      <c r="W53" s="51" t="n"/>
-      <c r="X53" s="51" t="n"/>
-      <c r="Y53" s="51" t="n"/>
-      <c r="Z53" s="51" t="n"/>
-      <c r="AA53" s="51" t="n"/>
-      <c r="AB53" s="51" t="n"/>
+      <c r="A53" s="53" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B53" s="54" t="inlineStr">
+        <is>
+          <t>宋增辉</t>
+        </is>
+      </c>
+      <c r="C53" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D53" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E53" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F53" s="55">
+        <f>G53+H53+I53</f>
+        <v/>
+      </c>
+      <c r="G53" s="55">
+        <f>Q53+R53</f>
+        <v/>
+      </c>
+      <c r="H53" s="55">
+        <f>U53-V53</f>
+        <v/>
+      </c>
+      <c r="I53" s="55">
+        <f>AB53</f>
+        <v/>
+      </c>
+      <c r="J53" s="55" t="n">
+        <v>283600</v>
+      </c>
+      <c r="K53" s="55" t="n">
+        <v>103232</v>
+      </c>
+      <c r="L53" s="55" t="n">
+        <v>113500</v>
+      </c>
+      <c r="M53" s="55" t="n">
+        <v>-10268</v>
+      </c>
+      <c r="N53" s="56" t="n">
+        <v>-0.0362059238363893</v>
+      </c>
+      <c r="O53" s="55" t="n"/>
+      <c r="P53" s="56" t="n"/>
+      <c r="Q53" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="55" t="n"/>
+      <c r="S53" s="55" t="n"/>
+      <c r="T53" s="56" t="n"/>
+      <c r="U53" s="55" t="n"/>
+      <c r="V53" s="55" t="n"/>
+      <c r="W53" s="55" t="n"/>
+      <c r="X53" s="55" t="n"/>
+      <c r="Y53" s="55" t="n"/>
+      <c r="Z53" s="55" t="n"/>
+      <c r="AA53" s="56" t="n"/>
+      <c r="AB53" s="55" t="n">
+        <v>0</v>
+      </c>
       <c r="AC53" s="51" t="n"/>
       <c r="AD53" s="51" t="n"/>
       <c r="AE53" s="51" t="n"/>
@@ -31195,34 +31329,80 @@
       <c r="AT53" s="51" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="51" t="n"/>
-      <c r="B54" s="51" t="n"/>
-      <c r="C54" s="51" t="n"/>
-      <c r="D54" s="51" t="n"/>
-      <c r="E54" s="51" t="n"/>
-      <c r="F54" s="51" t="n"/>
-      <c r="G54" s="51" t="n"/>
-      <c r="H54" s="51" t="n"/>
-      <c r="I54" s="51" t="n"/>
-      <c r="J54" s="51" t="n"/>
-      <c r="K54" s="51" t="n"/>
-      <c r="L54" s="51" t="n"/>
-      <c r="M54" s="51" t="n"/>
-      <c r="N54" s="51" t="n"/>
-      <c r="O54" s="51" t="n"/>
-      <c r="P54" s="51" t="n"/>
-      <c r="Q54" s="51" t="n"/>
-      <c r="R54" s="51" t="n"/>
-      <c r="S54" s="51" t="n"/>
-      <c r="T54" s="51" t="n"/>
-      <c r="U54" s="51" t="n"/>
-      <c r="V54" s="51" t="n"/>
-      <c r="W54" s="51" t="n"/>
-      <c r="X54" s="51" t="n"/>
-      <c r="Y54" s="51" t="n"/>
-      <c r="Z54" s="51" t="n"/>
-      <c r="AA54" s="51" t="n"/>
-      <c r="AB54" s="51" t="n"/>
+      <c r="A54" s="53" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B54" s="54" t="inlineStr">
+        <is>
+          <t>田一禾</t>
+        </is>
+      </c>
+      <c r="C54" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D54" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E54" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F54" s="55">
+        <f>G54+H54+I54</f>
+        <v/>
+      </c>
+      <c r="G54" s="55">
+        <f>Q54+R54</f>
+        <v/>
+      </c>
+      <c r="H54" s="55">
+        <f>U54-V54</f>
+        <v/>
+      </c>
+      <c r="I54" s="55">
+        <f>AB54</f>
+        <v/>
+      </c>
+      <c r="J54" s="55" t="n">
+        <v>283600</v>
+      </c>
+      <c r="K54" s="55" t="n">
+        <v>414051</v>
+      </c>
+      <c r="L54" s="55" t="n">
+        <v>16812</v>
+      </c>
+      <c r="M54" s="55" t="n">
+        <v>397239</v>
+      </c>
+      <c r="N54" s="56" t="n">
+        <v>1.40070169252468</v>
+      </c>
+      <c r="O54" s="55" t="n"/>
+      <c r="P54" s="56" t="n"/>
+      <c r="Q54" s="55" t="n">
+        <v>15878.5</v>
+      </c>
+      <c r="R54" s="55" t="n"/>
+      <c r="S54" s="55" t="n"/>
+      <c r="T54" s="56" t="n"/>
+      <c r="U54" s="55" t="n">
+        <v>994.5</v>
+      </c>
+      <c r="V54" s="55" t="n"/>
+      <c r="W54" s="55" t="n"/>
+      <c r="X54" s="55" t="n"/>
+      <c r="Y54" s="55" t="n"/>
+      <c r="Z54" s="55" t="n"/>
+      <c r="AA54" s="56" t="n"/>
+      <c r="AB54" s="55" t="n">
+        <v>1550</v>
+      </c>
       <c r="AC54" s="51" t="n"/>
       <c r="AD54" s="51" t="n"/>
       <c r="AE54" s="51" t="n"/>
@@ -31243,34 +31423,80 @@
       <c r="AT54" s="51" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="51" t="n"/>
-      <c r="B55" s="51" t="n"/>
-      <c r="C55" s="51" t="n"/>
-      <c r="D55" s="51" t="n"/>
-      <c r="E55" s="51" t="n"/>
-      <c r="F55" s="51" t="n"/>
-      <c r="G55" s="51" t="n"/>
-      <c r="H55" s="51" t="n"/>
-      <c r="I55" s="51" t="n"/>
-      <c r="J55" s="51" t="n"/>
-      <c r="K55" s="51" t="n"/>
-      <c r="L55" s="51" t="n"/>
-      <c r="M55" s="51" t="n"/>
-      <c r="N55" s="51" t="n"/>
-      <c r="O55" s="51" t="n"/>
-      <c r="P55" s="51" t="n"/>
-      <c r="Q55" s="51" t="n"/>
-      <c r="R55" s="51" t="n"/>
-      <c r="S55" s="51" t="n"/>
-      <c r="T55" s="51" t="n"/>
-      <c r="U55" s="51" t="n"/>
-      <c r="V55" s="51" t="n"/>
-      <c r="W55" s="51" t="n"/>
-      <c r="X55" s="51" t="n"/>
-      <c r="Y55" s="51" t="n"/>
-      <c r="Z55" s="51" t="n"/>
-      <c r="AA55" s="51" t="n"/>
-      <c r="AB55" s="51" t="n"/>
+      <c r="A55" s="53" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B55" s="54" t="inlineStr">
+        <is>
+          <t>黄智超</t>
+        </is>
+      </c>
+      <c r="C55" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D55" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E55" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F55" s="55">
+        <f>G55+H55+I55</f>
+        <v/>
+      </c>
+      <c r="G55" s="55">
+        <f>Q55+R55</f>
+        <v/>
+      </c>
+      <c r="H55" s="55">
+        <f>U55-V55</f>
+        <v/>
+      </c>
+      <c r="I55" s="55">
+        <f>AB55</f>
+        <v/>
+      </c>
+      <c r="J55" s="55" t="n">
+        <v>283600</v>
+      </c>
+      <c r="K55" s="55" t="n">
+        <v>431176.45</v>
+      </c>
+      <c r="L55" s="55" t="n">
+        <v>193036.3</v>
+      </c>
+      <c r="M55" s="55" t="n">
+        <v>238140.15</v>
+      </c>
+      <c r="N55" s="56" t="n">
+        <v>0.839704337094499</v>
+      </c>
+      <c r="O55" s="55" t="n"/>
+      <c r="P55" s="56" t="n"/>
+      <c r="Q55" s="55" t="n">
+        <v>4387.3256</v>
+      </c>
+      <c r="R55" s="55" t="n"/>
+      <c r="S55" s="55" t="n"/>
+      <c r="T55" s="56" t="n"/>
+      <c r="U55" s="55" t="n">
+        <v>648.6744</v>
+      </c>
+      <c r="V55" s="55" t="n"/>
+      <c r="W55" s="55" t="n"/>
+      <c r="X55" s="55" t="n"/>
+      <c r="Y55" s="55" t="n"/>
+      <c r="Z55" s="55" t="n"/>
+      <c r="AA55" s="56" t="n"/>
+      <c r="AB55" s="55" t="n">
+        <v>2000</v>
+      </c>
       <c r="AC55" s="51" t="n"/>
       <c r="AD55" s="51" t="n"/>
       <c r="AE55" s="51" t="n"/>
@@ -31291,34 +31517,78 @@
       <c r="AT55" s="51" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="51" t="n"/>
-      <c r="B56" s="51" t="n"/>
-      <c r="C56" s="51" t="n"/>
-      <c r="D56" s="51" t="n"/>
-      <c r="E56" s="51" t="n"/>
-      <c r="F56" s="51" t="n"/>
-      <c r="G56" s="51" t="n"/>
-      <c r="H56" s="51" t="n"/>
-      <c r="I56" s="51" t="n"/>
-      <c r="J56" s="51" t="n"/>
-      <c r="K56" s="51" t="n"/>
-      <c r="L56" s="51" t="n"/>
-      <c r="M56" s="51" t="n"/>
-      <c r="N56" s="51" t="n"/>
-      <c r="O56" s="51" t="n"/>
-      <c r="P56" s="51" t="n"/>
-      <c r="Q56" s="51" t="n"/>
-      <c r="R56" s="51" t="n"/>
-      <c r="S56" s="51" t="n"/>
-      <c r="T56" s="51" t="n"/>
-      <c r="U56" s="51" t="n"/>
-      <c r="V56" s="51" t="n"/>
-      <c r="W56" s="51" t="n"/>
-      <c r="X56" s="51" t="n"/>
-      <c r="Y56" s="51" t="n"/>
-      <c r="Z56" s="51" t="n"/>
-      <c r="AA56" s="51" t="n"/>
-      <c r="AB56" s="51" t="n"/>
+      <c r="A56" s="53" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B56" s="54" t="inlineStr">
+        <is>
+          <t>徐一城</t>
+        </is>
+      </c>
+      <c r="C56" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D56" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E56" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F56" s="55">
+        <f>G56+H56+I56</f>
+        <v/>
+      </c>
+      <c r="G56" s="55">
+        <f>Q56+R56</f>
+        <v/>
+      </c>
+      <c r="H56" s="55">
+        <f>U56-V56</f>
+        <v/>
+      </c>
+      <c r="I56" s="55">
+        <f>AB56</f>
+        <v/>
+      </c>
+      <c r="J56" s="55" t="n">
+        <v>283600</v>
+      </c>
+      <c r="K56" s="55" t="n">
+        <v>410615</v>
+      </c>
+      <c r="L56" s="55" t="n">
+        <v>40675</v>
+      </c>
+      <c r="M56" s="55" t="n">
+        <v>369940</v>
+      </c>
+      <c r="N56" s="56" t="n">
+        <v>1.30444287729196</v>
+      </c>
+      <c r="O56" s="55" t="n"/>
+      <c r="P56" s="56" t="n"/>
+      <c r="Q56" s="55" t="n">
+        <v>14870</v>
+      </c>
+      <c r="R56" s="55" t="n"/>
+      <c r="S56" s="55" t="n"/>
+      <c r="T56" s="56" t="n"/>
+      <c r="U56" s="55" t="n"/>
+      <c r="V56" s="55" t="n"/>
+      <c r="W56" s="55" t="n"/>
+      <c r="X56" s="55" t="n"/>
+      <c r="Y56" s="55" t="n"/>
+      <c r="Z56" s="55" t="n"/>
+      <c r="AA56" s="56" t="n"/>
+      <c r="AB56" s="55" t="n">
+        <v>1681</v>
+      </c>
       <c r="AC56" s="51" t="n"/>
       <c r="AD56" s="51" t="n"/>
       <c r="AE56" s="51" t="n"/>
@@ -31339,34 +31609,80 @@
       <c r="AT56" s="51" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="51" t="n"/>
-      <c r="B57" s="51" t="n"/>
-      <c r="C57" s="51" t="n"/>
-      <c r="D57" s="51" t="n"/>
-      <c r="E57" s="51" t="n"/>
-      <c r="F57" s="51" t="n"/>
-      <c r="G57" s="51" t="n"/>
-      <c r="H57" s="51" t="n"/>
-      <c r="I57" s="51" t="n"/>
-      <c r="J57" s="51" t="n"/>
-      <c r="K57" s="51" t="n"/>
-      <c r="L57" s="51" t="n"/>
-      <c r="M57" s="51" t="n"/>
-      <c r="N57" s="51" t="n"/>
-      <c r="O57" s="51" t="n"/>
-      <c r="P57" s="51" t="n"/>
-      <c r="Q57" s="51" t="n"/>
-      <c r="R57" s="51" t="n"/>
-      <c r="S57" s="51" t="n"/>
-      <c r="T57" s="51" t="n"/>
-      <c r="U57" s="51" t="n"/>
-      <c r="V57" s="51" t="n"/>
-      <c r="W57" s="51" t="n"/>
-      <c r="X57" s="51" t="n"/>
-      <c r="Y57" s="51" t="n"/>
-      <c r="Z57" s="51" t="n"/>
-      <c r="AA57" s="51" t="n"/>
-      <c r="AB57" s="51" t="n"/>
+      <c r="A57" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B57" s="54" t="inlineStr">
+        <is>
+          <t>刘晓娟</t>
+        </is>
+      </c>
+      <c r="C57" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D57" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E57" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F57" s="55">
+        <f>G57+H57+I57</f>
+        <v/>
+      </c>
+      <c r="G57" s="55">
+        <f>Q57+R57</f>
+        <v/>
+      </c>
+      <c r="H57" s="55">
+        <f>U57-V57</f>
+        <v/>
+      </c>
+      <c r="I57" s="55">
+        <f>AB57</f>
+        <v/>
+      </c>
+      <c r="J57" s="55" t="n">
+        <v>792135</v>
+      </c>
+      <c r="K57" s="55" t="n">
+        <v>1086040.2</v>
+      </c>
+      <c r="L57" s="55" t="n">
+        <v>43061.4</v>
+      </c>
+      <c r="M57" s="55" t="n">
+        <v>1042978.8</v>
+      </c>
+      <c r="N57" s="56" t="n">
+        <v>1.3166679921983</v>
+      </c>
+      <c r="O57" s="55" t="n"/>
+      <c r="P57" s="56" t="n"/>
+      <c r="Q57" s="55" t="n">
+        <v>41840.3024</v>
+      </c>
+      <c r="R57" s="55" t="n"/>
+      <c r="S57" s="55" t="n"/>
+      <c r="T57" s="56" t="n"/>
+      <c r="U57" s="55" t="n">
+        <v>4673.979</v>
+      </c>
+      <c r="V57" s="55" t="n"/>
+      <c r="W57" s="55" t="n"/>
+      <c r="X57" s="55" t="n"/>
+      <c r="Y57" s="55" t="n"/>
+      <c r="Z57" s="55" t="n"/>
+      <c r="AA57" s="56" t="n"/>
+      <c r="AB57" s="55" t="n">
+        <v>2000</v>
+      </c>
       <c r="AC57" s="51" t="n"/>
       <c r="AD57" s="51" t="n"/>
       <c r="AE57" s="51" t="n"/>
@@ -31387,34 +31703,80 @@
       <c r="AT57" s="51" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="51" t="n"/>
-      <c r="B58" s="51" t="n"/>
-      <c r="C58" s="51" t="n"/>
-      <c r="D58" s="51" t="n"/>
-      <c r="E58" s="51" t="n"/>
-      <c r="F58" s="51" t="n"/>
-      <c r="G58" s="51" t="n"/>
-      <c r="H58" s="51" t="n"/>
-      <c r="I58" s="51" t="n"/>
-      <c r="J58" s="51" t="n"/>
-      <c r="K58" s="51" t="n"/>
-      <c r="L58" s="51" t="n"/>
-      <c r="M58" s="51" t="n"/>
-      <c r="N58" s="51" t="n"/>
-      <c r="O58" s="51" t="n"/>
-      <c r="P58" s="51" t="n"/>
-      <c r="Q58" s="51" t="n"/>
-      <c r="R58" s="51" t="n"/>
-      <c r="S58" s="51" t="n"/>
-      <c r="T58" s="51" t="n"/>
-      <c r="U58" s="51" t="n"/>
-      <c r="V58" s="51" t="n"/>
-      <c r="W58" s="51" t="n"/>
-      <c r="X58" s="51" t="n"/>
-      <c r="Y58" s="51" t="n"/>
-      <c r="Z58" s="51" t="n"/>
-      <c r="AA58" s="51" t="n"/>
-      <c r="AB58" s="51" t="n"/>
+      <c r="A58" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B58" s="54" t="inlineStr">
+        <is>
+          <t>房国超</t>
+        </is>
+      </c>
+      <c r="C58" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D58" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E58" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F58" s="55">
+        <f>G58+H58+I58</f>
+        <v/>
+      </c>
+      <c r="G58" s="55">
+        <f>Q58+R58</f>
+        <v/>
+      </c>
+      <c r="H58" s="55">
+        <f>U58-V58</f>
+        <v/>
+      </c>
+      <c r="I58" s="55">
+        <f>AB58</f>
+        <v/>
+      </c>
+      <c r="J58" s="55" t="n">
+        <v>968165</v>
+      </c>
+      <c r="K58" s="55" t="n">
+        <v>799243.5</v>
+      </c>
+      <c r="L58" s="55" t="n">
+        <v>22865</v>
+      </c>
+      <c r="M58" s="55" t="n">
+        <v>776378.5</v>
+      </c>
+      <c r="N58" s="56" t="n">
+        <v>0.801907216228639</v>
+      </c>
+      <c r="O58" s="55" t="n"/>
+      <c r="P58" s="56" t="n"/>
+      <c r="Q58" s="55" t="n">
+        <v>13989.813</v>
+      </c>
+      <c r="R58" s="55" t="n"/>
+      <c r="S58" s="55" t="n"/>
+      <c r="T58" s="56" t="n"/>
+      <c r="U58" s="55" t="n">
+        <v>213.2622</v>
+      </c>
+      <c r="V58" s="55" t="n"/>
+      <c r="W58" s="55" t="n"/>
+      <c r="X58" s="55" t="n"/>
+      <c r="Y58" s="55" t="n"/>
+      <c r="Z58" s="55" t="n"/>
+      <c r="AA58" s="56" t="n"/>
+      <c r="AB58" s="55" t="n">
+        <v>0</v>
+      </c>
       <c r="AC58" s="51" t="n"/>
       <c r="AD58" s="51" t="n"/>
       <c r="AE58" s="51" t="n"/>
@@ -31435,34 +31797,78 @@
       <c r="AT58" s="51" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="51" t="n"/>
-      <c r="B59" s="51" t="n"/>
-      <c r="C59" s="51" t="n"/>
-      <c r="D59" s="51" t="n"/>
-      <c r="E59" s="51" t="n"/>
-      <c r="F59" s="51" t="n"/>
-      <c r="G59" s="51" t="n"/>
-      <c r="H59" s="51" t="n"/>
-      <c r="I59" s="51" t="n"/>
-      <c r="J59" s="51" t="n"/>
-      <c r="K59" s="51" t="n"/>
-      <c r="L59" s="51" t="n"/>
-      <c r="M59" s="51" t="n"/>
-      <c r="N59" s="51" t="n"/>
-      <c r="O59" s="51" t="n"/>
-      <c r="P59" s="51" t="n"/>
-      <c r="Q59" s="51" t="n"/>
-      <c r="R59" s="51" t="n"/>
-      <c r="S59" s="51" t="n"/>
-      <c r="T59" s="51" t="n"/>
-      <c r="U59" s="51" t="n"/>
-      <c r="V59" s="51" t="n"/>
-      <c r="W59" s="51" t="n"/>
-      <c r="X59" s="51" t="n"/>
-      <c r="Y59" s="51" t="n"/>
-      <c r="Z59" s="51" t="n"/>
-      <c r="AA59" s="51" t="n"/>
-      <c r="AB59" s="51" t="n"/>
+      <c r="A59" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B59" s="54" t="inlineStr">
+        <is>
+          <t>王磊</t>
+        </is>
+      </c>
+      <c r="C59" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D59" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E59" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F59" s="55">
+        <f>G59+H59+I59</f>
+        <v/>
+      </c>
+      <c r="G59" s="55">
+        <f>Q59+R59</f>
+        <v/>
+      </c>
+      <c r="H59" s="55">
+        <f>U59-V59</f>
+        <v/>
+      </c>
+      <c r="I59" s="55">
+        <f>AB59</f>
+        <v/>
+      </c>
+      <c r="J59" s="55" t="n">
+        <v>320000</v>
+      </c>
+      <c r="K59" s="55" t="n">
+        <v>411200.5</v>
+      </c>
+      <c r="L59" s="55" t="n">
+        <v>40842.1</v>
+      </c>
+      <c r="M59" s="55" t="n">
+        <v>370358.4</v>
+      </c>
+      <c r="N59" s="56" t="n">
+        <v>1.15737</v>
+      </c>
+      <c r="O59" s="55" t="n"/>
+      <c r="P59" s="56" t="n"/>
+      <c r="Q59" s="55" t="n">
+        <v>11110.752</v>
+      </c>
+      <c r="R59" s="55" t="n"/>
+      <c r="S59" s="55" t="n"/>
+      <c r="T59" s="56" t="n"/>
+      <c r="U59" s="55" t="n"/>
+      <c r="V59" s="55" t="n"/>
+      <c r="W59" s="55" t="n"/>
+      <c r="X59" s="55" t="n"/>
+      <c r="Y59" s="55" t="n"/>
+      <c r="Z59" s="55" t="n"/>
+      <c r="AA59" s="56" t="n"/>
+      <c r="AB59" s="55" t="n">
+        <v>2000</v>
+      </c>
       <c r="AC59" s="51" t="n"/>
       <c r="AD59" s="51" t="n"/>
       <c r="AE59" s="51" t="n"/>
@@ -31483,34 +31889,78 @@
       <c r="AT59" s="51" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="51" t="n"/>
-      <c r="B60" s="51" t="n"/>
-      <c r="C60" s="51" t="n"/>
-      <c r="D60" s="51" t="n"/>
-      <c r="E60" s="51" t="n"/>
-      <c r="F60" s="51" t="n"/>
-      <c r="G60" s="51" t="n"/>
-      <c r="H60" s="51" t="n"/>
-      <c r="I60" s="51" t="n"/>
-      <c r="J60" s="51" t="n"/>
-      <c r="K60" s="51" t="n"/>
-      <c r="L60" s="51" t="n"/>
-      <c r="M60" s="51" t="n"/>
-      <c r="N60" s="51" t="n"/>
-      <c r="O60" s="51" t="n"/>
-      <c r="P60" s="51" t="n"/>
-      <c r="Q60" s="51" t="n"/>
-      <c r="R60" s="51" t="n"/>
-      <c r="S60" s="51" t="n"/>
-      <c r="T60" s="51" t="n"/>
-      <c r="U60" s="51" t="n"/>
-      <c r="V60" s="51" t="n"/>
-      <c r="W60" s="51" t="n"/>
-      <c r="X60" s="51" t="n"/>
-      <c r="Y60" s="51" t="n"/>
-      <c r="Z60" s="51" t="n"/>
-      <c r="AA60" s="51" t="n"/>
-      <c r="AB60" s="51" t="n"/>
+      <c r="A60" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B60" s="54" t="inlineStr">
+        <is>
+          <t>田一禾</t>
+        </is>
+      </c>
+      <c r="C60" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D60" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E60" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F60" s="55">
+        <f>G60+H60+I60</f>
+        <v/>
+      </c>
+      <c r="G60" s="55">
+        <f>Q60+R60</f>
+        <v/>
+      </c>
+      <c r="H60" s="55">
+        <f>U60-V60</f>
+        <v/>
+      </c>
+      <c r="I60" s="55">
+        <f>AB60</f>
+        <v/>
+      </c>
+      <c r="J60" s="55" t="n">
+        <v>792135</v>
+      </c>
+      <c r="K60" s="55" t="n">
+        <v>1179016</v>
+      </c>
+      <c r="L60" s="55" t="n">
+        <v>121576.3</v>
+      </c>
+      <c r="M60" s="55" t="n">
+        <v>1057439.7</v>
+      </c>
+      <c r="N60" s="56" t="n">
+        <v>1.33492359256945</v>
+      </c>
+      <c r="O60" s="55" t="n"/>
+      <c r="P60" s="56" t="n"/>
+      <c r="Q60" s="55" t="n">
+        <v>42297.588</v>
+      </c>
+      <c r="R60" s="55" t="n"/>
+      <c r="S60" s="55" t="n"/>
+      <c r="T60" s="56" t="n"/>
+      <c r="U60" s="55" t="n"/>
+      <c r="V60" s="55" t="n"/>
+      <c r="W60" s="55" t="n"/>
+      <c r="X60" s="55" t="n"/>
+      <c r="Y60" s="55" t="n"/>
+      <c r="Z60" s="55" t="n"/>
+      <c r="AA60" s="56" t="n"/>
+      <c r="AB60" s="55" t="n">
+        <v>2000</v>
+      </c>
       <c r="AC60" s="51" t="n"/>
       <c r="AD60" s="51" t="n"/>
       <c r="AE60" s="51" t="n"/>
@@ -31531,34 +31981,80 @@
       <c r="AT60" s="51" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="51" t="n"/>
-      <c r="B61" s="51" t="n"/>
-      <c r="C61" s="51" t="n"/>
-      <c r="D61" s="51" t="n"/>
-      <c r="E61" s="51" t="n"/>
-      <c r="F61" s="51" t="n"/>
-      <c r="G61" s="51" t="n"/>
-      <c r="H61" s="51" t="n"/>
-      <c r="I61" s="51" t="n"/>
-      <c r="J61" s="51" t="n"/>
-      <c r="K61" s="51" t="n"/>
-      <c r="L61" s="51" t="n"/>
-      <c r="M61" s="51" t="n"/>
-      <c r="N61" s="51" t="n"/>
-      <c r="O61" s="51" t="n"/>
-      <c r="P61" s="51" t="n"/>
-      <c r="Q61" s="51" t="n"/>
-      <c r="R61" s="51" t="n"/>
-      <c r="S61" s="51" t="n"/>
-      <c r="T61" s="51" t="n"/>
-      <c r="U61" s="51" t="n"/>
-      <c r="V61" s="51" t="n"/>
-      <c r="W61" s="51" t="n"/>
-      <c r="X61" s="51" t="n"/>
-      <c r="Y61" s="51" t="n"/>
-      <c r="Z61" s="51" t="n"/>
-      <c r="AA61" s="51" t="n"/>
-      <c r="AB61" s="51" t="n"/>
+      <c r="A61" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B61" s="54" t="inlineStr">
+        <is>
+          <t>黄智超</t>
+        </is>
+      </c>
+      <c r="C61" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D61" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E61" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F61" s="55">
+        <f>G61+H61+I61</f>
+        <v/>
+      </c>
+      <c r="G61" s="55">
+        <f>Q61+R61</f>
+        <v/>
+      </c>
+      <c r="H61" s="55">
+        <f>U61-V61</f>
+        <v/>
+      </c>
+      <c r="I61" s="55">
+        <f>AB61</f>
+        <v/>
+      </c>
+      <c r="J61" s="55" t="n">
+        <v>968165</v>
+      </c>
+      <c r="K61" s="55" t="n">
+        <v>1848728</v>
+      </c>
+      <c r="L61" s="55" t="n">
+        <v>135631.5</v>
+      </c>
+      <c r="M61" s="55" t="n">
+        <v>1713096.5</v>
+      </c>
+      <c r="N61" s="56" t="n">
+        <v>1.76942618252054</v>
+      </c>
+      <c r="O61" s="55" t="n"/>
+      <c r="P61" s="56" t="n"/>
+      <c r="Q61" s="55" t="n">
+        <v>68528.84</v>
+      </c>
+      <c r="R61" s="55" t="n"/>
+      <c r="S61" s="55" t="n"/>
+      <c r="T61" s="56" t="n"/>
+      <c r="U61" s="55" t="n">
+        <v>1893</v>
+      </c>
+      <c r="V61" s="55" t="n"/>
+      <c r="W61" s="55" t="n"/>
+      <c r="X61" s="55" t="n"/>
+      <c r="Y61" s="55" t="n"/>
+      <c r="Z61" s="55" t="n"/>
+      <c r="AA61" s="56" t="n"/>
+      <c r="AB61" s="55" t="n">
+        <v>2000</v>
+      </c>
       <c r="AC61" s="51" t="n"/>
       <c r="AD61" s="51" t="n"/>
       <c r="AE61" s="51" t="n"/>
@@ -31579,34 +32075,80 @@
       <c r="AT61" s="51" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="51" t="n"/>
-      <c r="B62" s="51" t="n"/>
-      <c r="C62" s="51" t="n"/>
-      <c r="D62" s="51" t="n"/>
-      <c r="E62" s="51" t="n"/>
-      <c r="F62" s="51" t="n"/>
-      <c r="G62" s="51" t="n"/>
-      <c r="H62" s="51" t="n"/>
-      <c r="I62" s="51" t="n"/>
-      <c r="J62" s="51" t="n"/>
-      <c r="K62" s="51" t="n"/>
-      <c r="L62" s="51" t="n"/>
-      <c r="M62" s="51" t="n"/>
-      <c r="N62" s="51" t="n"/>
-      <c r="O62" s="51" t="n"/>
-      <c r="P62" s="51" t="n"/>
-      <c r="Q62" s="51" t="n"/>
-      <c r="R62" s="51" t="n"/>
-      <c r="S62" s="51" t="n"/>
-      <c r="T62" s="51" t="n"/>
-      <c r="U62" s="51" t="n"/>
-      <c r="V62" s="51" t="n"/>
-      <c r="W62" s="51" t="n"/>
-      <c r="X62" s="51" t="n"/>
-      <c r="Y62" s="51" t="n"/>
-      <c r="Z62" s="51" t="n"/>
-      <c r="AA62" s="51" t="n"/>
-      <c r="AB62" s="51" t="n"/>
+      <c r="A62" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B62" s="54" t="inlineStr">
+        <is>
+          <t>姚斯元</t>
+        </is>
+      </c>
+      <c r="C62" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D62" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E62" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F62" s="55">
+        <f>G62+H62+I62</f>
+        <v/>
+      </c>
+      <c r="G62" s="55">
+        <f>Q62+R62</f>
+        <v/>
+      </c>
+      <c r="H62" s="55">
+        <f>U62-V62</f>
+        <v/>
+      </c>
+      <c r="I62" s="55">
+        <f>AB62</f>
+        <v/>
+      </c>
+      <c r="J62" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="55" t="n">
+        <v>21604</v>
+      </c>
+      <c r="L62" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="55" t="n">
+        <v>21604</v>
+      </c>
+      <c r="N62" s="56" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="O62" s="55" t="n"/>
+      <c r="P62" s="56" t="n"/>
+      <c r="Q62" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="55" t="n"/>
+      <c r="S62" s="55" t="n"/>
+      <c r="T62" s="56" t="n"/>
+      <c r="U62" s="55" t="n"/>
+      <c r="V62" s="55" t="n"/>
+      <c r="W62" s="55" t="n"/>
+      <c r="X62" s="55" t="n"/>
+      <c r="Y62" s="55" t="n"/>
+      <c r="Z62" s="55" t="n"/>
+      <c r="AA62" s="56" t="n"/>
+      <c r="AB62" s="55" t="n">
+        <v>3610</v>
+      </c>
       <c r="AC62" s="51" t="n"/>
       <c r="AD62" s="51" t="n"/>
       <c r="AE62" s="51" t="n"/>
@@ -31627,34 +32169,78 @@
       <c r="AT62" s="51" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="51" t="n"/>
-      <c r="B63" s="51" t="n"/>
-      <c r="C63" s="51" t="n"/>
-      <c r="D63" s="51" t="n"/>
-      <c r="E63" s="51" t="n"/>
-      <c r="F63" s="51" t="n"/>
-      <c r="G63" s="51" t="n"/>
-      <c r="H63" s="51" t="n"/>
-      <c r="I63" s="51" t="n"/>
-      <c r="J63" s="51" t="n"/>
-      <c r="K63" s="51" t="n"/>
-      <c r="L63" s="51" t="n"/>
-      <c r="M63" s="51" t="n"/>
-      <c r="N63" s="51" t="n"/>
-      <c r="O63" s="51" t="n"/>
-      <c r="P63" s="51" t="n"/>
-      <c r="Q63" s="51" t="n"/>
-      <c r="R63" s="51" t="n"/>
-      <c r="S63" s="51" t="n"/>
-      <c r="T63" s="51" t="n"/>
-      <c r="U63" s="51" t="n"/>
-      <c r="V63" s="51" t="n"/>
-      <c r="W63" s="51" t="n"/>
-      <c r="X63" s="51" t="n"/>
-      <c r="Y63" s="51" t="n"/>
-      <c r="Z63" s="51" t="n"/>
-      <c r="AA63" s="51" t="n"/>
-      <c r="AB63" s="51" t="n"/>
+      <c r="A63" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B63" s="54" t="inlineStr">
+        <is>
+          <t>徐振东</t>
+        </is>
+      </c>
+      <c r="C63" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D63" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E63" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F63" s="55">
+        <f>G63+H63+I63</f>
+        <v/>
+      </c>
+      <c r="G63" s="55">
+        <f>Q63+R63</f>
+        <v/>
+      </c>
+      <c r="H63" s="55">
+        <f>U63-V63</f>
+        <v/>
+      </c>
+      <c r="I63" s="55">
+        <f>AB63</f>
+        <v/>
+      </c>
+      <c r="J63" s="55" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K63" s="55" t="n">
+        <v>30480.5</v>
+      </c>
+      <c r="L63" s="55" t="n">
+        <v>5680</v>
+      </c>
+      <c r="M63" s="55" t="n">
+        <v>24800.5</v>
+      </c>
+      <c r="N63" s="56" t="n">
+        <v>0.248005</v>
+      </c>
+      <c r="O63" s="55" t="n"/>
+      <c r="P63" s="56" t="n"/>
+      <c r="Q63" s="55" t="n">
+        <v>3000</v>
+      </c>
+      <c r="R63" s="55" t="n"/>
+      <c r="S63" s="55" t="n"/>
+      <c r="T63" s="56" t="n"/>
+      <c r="U63" s="55" t="n"/>
+      <c r="V63" s="55" t="n"/>
+      <c r="W63" s="55" t="n"/>
+      <c r="X63" s="55" t="n"/>
+      <c r="Y63" s="55" t="n"/>
+      <c r="Z63" s="55" t="n"/>
+      <c r="AA63" s="56" t="n"/>
+      <c r="AB63" s="55" t="n">
+        <v>2000</v>
+      </c>
       <c r="AC63" s="51" t="n"/>
       <c r="AD63" s="51" t="n"/>
       <c r="AE63" s="51" t="n"/>
@@ -31675,34 +32261,80 @@
       <c r="AT63" s="51" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="51" t="n"/>
-      <c r="B64" s="51" t="n"/>
-      <c r="C64" s="51" t="n"/>
-      <c r="D64" s="51" t="n"/>
-      <c r="E64" s="51" t="n"/>
-      <c r="F64" s="51" t="n"/>
-      <c r="G64" s="51" t="n"/>
-      <c r="H64" s="51" t="n"/>
-      <c r="I64" s="51" t="n"/>
-      <c r="J64" s="51" t="n"/>
-      <c r="K64" s="51" t="n"/>
-      <c r="L64" s="51" t="n"/>
-      <c r="M64" s="51" t="n"/>
-      <c r="N64" s="51" t="n"/>
-      <c r="O64" s="51" t="n"/>
-      <c r="P64" s="51" t="n"/>
-      <c r="Q64" s="51" t="n"/>
-      <c r="R64" s="51" t="n"/>
-      <c r="S64" s="51" t="n"/>
-      <c r="T64" s="51" t="n"/>
-      <c r="U64" s="51" t="n"/>
-      <c r="V64" s="51" t="n"/>
-      <c r="W64" s="51" t="n"/>
-      <c r="X64" s="51" t="n"/>
-      <c r="Y64" s="51" t="n"/>
-      <c r="Z64" s="51" t="n"/>
-      <c r="AA64" s="51" t="n"/>
-      <c r="AB64" s="51" t="n"/>
+      <c r="A64" s="53" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B64" s="54" t="inlineStr">
+        <is>
+          <t>徐晗</t>
+        </is>
+      </c>
+      <c r="C64" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D64" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E64" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F64" s="55">
+        <f>G64+H64+I64</f>
+        <v/>
+      </c>
+      <c r="G64" s="55">
+        <f>Q64+R64</f>
+        <v/>
+      </c>
+      <c r="H64" s="55">
+        <f>U64-V64</f>
+        <v/>
+      </c>
+      <c r="I64" s="55">
+        <f>AB64</f>
+        <v/>
+      </c>
+      <c r="J64" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="55" t="n">
+        <v>47164</v>
+      </c>
+      <c r="L64" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="55" t="n">
+        <v>47164</v>
+      </c>
+      <c r="N64" s="56" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="O64" s="55" t="n"/>
+      <c r="P64" s="56" t="n"/>
+      <c r="Q64" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="55" t="n"/>
+      <c r="S64" s="55" t="n"/>
+      <c r="T64" s="56" t="n"/>
+      <c r="U64" s="55" t="n"/>
+      <c r="V64" s="55" t="n"/>
+      <c r="W64" s="55" t="n"/>
+      <c r="X64" s="55" t="n"/>
+      <c r="Y64" s="55" t="n"/>
+      <c r="Z64" s="55" t="n"/>
+      <c r="AA64" s="56" t="n"/>
+      <c r="AB64" s="55" t="n">
+        <v>4050</v>
+      </c>
       <c r="AC64" s="51" t="n"/>
       <c r="AD64" s="51" t="n"/>
       <c r="AE64" s="51" t="n"/>
@@ -31723,34 +32355,82 @@
       <c r="AT64" s="51" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="51" t="n"/>
-      <c r="B65" s="51" t="n"/>
-      <c r="C65" s="51" t="n"/>
-      <c r="D65" s="51" t="n"/>
-      <c r="E65" s="51" t="n"/>
-      <c r="F65" s="51" t="n"/>
-      <c r="G65" s="51" t="n"/>
-      <c r="H65" s="51" t="n"/>
-      <c r="I65" s="51" t="n"/>
-      <c r="J65" s="51" t="n"/>
-      <c r="K65" s="51" t="n"/>
-      <c r="L65" s="51" t="n"/>
-      <c r="M65" s="51" t="n"/>
-      <c r="N65" s="51" t="n"/>
-      <c r="O65" s="51" t="n"/>
-      <c r="P65" s="51" t="n"/>
-      <c r="Q65" s="51" t="n"/>
-      <c r="R65" s="51" t="n"/>
-      <c r="S65" s="51" t="n"/>
-      <c r="T65" s="51" t="n"/>
-      <c r="U65" s="51" t="n"/>
-      <c r="V65" s="51" t="n"/>
-      <c r="W65" s="51" t="n"/>
-      <c r="X65" s="51" t="n"/>
-      <c r="Y65" s="51" t="n"/>
-      <c r="Z65" s="51" t="n"/>
-      <c r="AA65" s="51" t="n"/>
-      <c r="AB65" s="51" t="n"/>
+      <c r="A65" s="53" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B65" s="54" t="inlineStr">
+        <is>
+          <t>刘晓娟</t>
+        </is>
+      </c>
+      <c r="C65" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D65" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E65" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F65" s="55">
+        <f>G65+H65+I65</f>
+        <v/>
+      </c>
+      <c r="G65" s="55">
+        <f>Q65+R65</f>
+        <v/>
+      </c>
+      <c r="H65" s="55">
+        <f>U65-V65</f>
+        <v/>
+      </c>
+      <c r="I65" s="55">
+        <f>AB65</f>
+        <v/>
+      </c>
+      <c r="J65" s="55" t="n">
+        <v>232142</v>
+      </c>
+      <c r="K65" s="55" t="n">
+        <v>420139.6</v>
+      </c>
+      <c r="L65" s="55" t="n">
+        <v>50569.1</v>
+      </c>
+      <c r="M65" s="55" t="n">
+        <v>369570.5</v>
+      </c>
+      <c r="N65" s="56" t="n">
+        <v>1.59200187816078</v>
+      </c>
+      <c r="O65" s="55" t="n"/>
+      <c r="P65" s="56" t="n"/>
+      <c r="Q65" s="55" t="n">
+        <v>18456.695</v>
+      </c>
+      <c r="R65" s="55" t="n"/>
+      <c r="S65" s="55" t="n"/>
+      <c r="T65" s="56" t="n"/>
+      <c r="U65" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="55" t="n">
+        <v>90</v>
+      </c>
+      <c r="W65" s="55" t="n"/>
+      <c r="X65" s="55" t="n"/>
+      <c r="Y65" s="55" t="n"/>
+      <c r="Z65" s="55" t="n"/>
+      <c r="AA65" s="56" t="n"/>
+      <c r="AB65" s="55" t="n">
+        <v>2000</v>
+      </c>
       <c r="AC65" s="51" t="n"/>
       <c r="AD65" s="51" t="n"/>
       <c r="AE65" s="51" t="n"/>
@@ -31771,34 +32451,78 @@
       <c r="AT65" s="51" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="51" t="n"/>
-      <c r="B66" s="51" t="n"/>
-      <c r="C66" s="51" t="n"/>
-      <c r="D66" s="51" t="n"/>
-      <c r="E66" s="51" t="n"/>
-      <c r="F66" s="51" t="n"/>
-      <c r="G66" s="51" t="n"/>
-      <c r="H66" s="51" t="n"/>
-      <c r="I66" s="51" t="n"/>
-      <c r="J66" s="51" t="n"/>
-      <c r="K66" s="51" t="n"/>
-      <c r="L66" s="51" t="n"/>
-      <c r="M66" s="51" t="n"/>
-      <c r="N66" s="51" t="n"/>
-      <c r="O66" s="51" t="n"/>
-      <c r="P66" s="51" t="n"/>
-      <c r="Q66" s="51" t="n"/>
-      <c r="R66" s="51" t="n"/>
-      <c r="S66" s="51" t="n"/>
-      <c r="T66" s="51" t="n"/>
-      <c r="U66" s="51" t="n"/>
-      <c r="V66" s="51" t="n"/>
-      <c r="W66" s="51" t="n"/>
-      <c r="X66" s="51" t="n"/>
-      <c r="Y66" s="51" t="n"/>
-      <c r="Z66" s="51" t="n"/>
-      <c r="AA66" s="51" t="n"/>
-      <c r="AB66" s="51" t="n"/>
+      <c r="A66" s="53" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B66" s="54" t="inlineStr">
+        <is>
+          <t>房国超</t>
+        </is>
+      </c>
+      <c r="C66" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D66" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E66" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F66" s="55">
+        <f>G66+H66+I66</f>
+        <v/>
+      </c>
+      <c r="G66" s="55">
+        <f>Q66+R66</f>
+        <v/>
+      </c>
+      <c r="H66" s="55">
+        <f>U66-V66</f>
+        <v/>
+      </c>
+      <c r="I66" s="55">
+        <f>AB66</f>
+        <v/>
+      </c>
+      <c r="J66" s="55" t="n">
+        <v>232142</v>
+      </c>
+      <c r="K66" s="55" t="n">
+        <v>551499</v>
+      </c>
+      <c r="L66" s="55" t="n">
+        <v>59029.1</v>
+      </c>
+      <c r="M66" s="55" t="n">
+        <v>492469.9</v>
+      </c>
+      <c r="N66" s="56" t="n">
+        <v>2.12141663292295</v>
+      </c>
+      <c r="O66" s="55" t="n"/>
+      <c r="P66" s="56" t="n"/>
+      <c r="Q66" s="55" t="n">
+        <v>24637.135</v>
+      </c>
+      <c r="R66" s="55" t="n"/>
+      <c r="S66" s="55" t="n"/>
+      <c r="T66" s="56" t="n"/>
+      <c r="U66" s="55" t="n"/>
+      <c r="V66" s="55" t="n"/>
+      <c r="W66" s="55" t="n"/>
+      <c r="X66" s="55" t="n"/>
+      <c r="Y66" s="55" t="n"/>
+      <c r="Z66" s="55" t="n"/>
+      <c r="AA66" s="56" t="n"/>
+      <c r="AB66" s="55" t="n">
+        <v>1700</v>
+      </c>
       <c r="AC66" s="51" t="n"/>
       <c r="AD66" s="51" t="n"/>
       <c r="AE66" s="51" t="n"/>
@@ -31819,34 +32543,78 @@
       <c r="AT66" s="51" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="51" t="n"/>
-      <c r="B67" s="51" t="n"/>
-      <c r="C67" s="51" t="n"/>
-      <c r="D67" s="51" t="n"/>
-      <c r="E67" s="51" t="n"/>
-      <c r="F67" s="51" t="n"/>
-      <c r="G67" s="51" t="n"/>
-      <c r="H67" s="51" t="n"/>
-      <c r="I67" s="51" t="n"/>
-      <c r="J67" s="51" t="n"/>
-      <c r="K67" s="51" t="n"/>
-      <c r="L67" s="51" t="n"/>
-      <c r="M67" s="51" t="n"/>
-      <c r="N67" s="51" t="n"/>
-      <c r="O67" s="51" t="n"/>
-      <c r="P67" s="51" t="n"/>
-      <c r="Q67" s="51" t="n"/>
-      <c r="R67" s="51" t="n"/>
-      <c r="S67" s="51" t="n"/>
-      <c r="T67" s="51" t="n"/>
-      <c r="U67" s="51" t="n"/>
-      <c r="V67" s="51" t="n"/>
-      <c r="W67" s="51" t="n"/>
-      <c r="X67" s="51" t="n"/>
-      <c r="Y67" s="51" t="n"/>
-      <c r="Z67" s="51" t="n"/>
-      <c r="AA67" s="51" t="n"/>
-      <c r="AB67" s="51" t="n"/>
+      <c r="A67" s="53" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B67" s="54" t="inlineStr">
+        <is>
+          <t>王磊</t>
+        </is>
+      </c>
+      <c r="C67" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D67" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E67" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F67" s="55">
+        <f>G67+H67+I67</f>
+        <v/>
+      </c>
+      <c r="G67" s="55">
+        <f>Q67+R67</f>
+        <v/>
+      </c>
+      <c r="H67" s="55">
+        <f>U67-V67</f>
+        <v/>
+      </c>
+      <c r="I67" s="55">
+        <f>AB67</f>
+        <v/>
+      </c>
+      <c r="J67" s="55" t="n">
+        <v>185714</v>
+      </c>
+      <c r="K67" s="55" t="n">
+        <v>216909.2</v>
+      </c>
+      <c r="L67" s="55" t="n">
+        <v>20691.2</v>
+      </c>
+      <c r="M67" s="55" t="n">
+        <v>196218</v>
+      </c>
+      <c r="N67" s="56" t="n">
+        <v>1.05656008701552</v>
+      </c>
+      <c r="O67" s="55" t="n"/>
+      <c r="P67" s="56" t="n"/>
+      <c r="Q67" s="55" t="n">
+        <v>5886.54</v>
+      </c>
+      <c r="R67" s="55" t="n"/>
+      <c r="S67" s="55" t="n"/>
+      <c r="T67" s="56" t="n"/>
+      <c r="U67" s="55" t="n"/>
+      <c r="V67" s="55" t="n"/>
+      <c r="W67" s="55" t="n"/>
+      <c r="X67" s="55" t="n"/>
+      <c r="Y67" s="55" t="n"/>
+      <c r="Z67" s="55" t="n"/>
+      <c r="AA67" s="56" t="n"/>
+      <c r="AB67" s="55" t="n">
+        <v>2000</v>
+      </c>
       <c r="AC67" s="51" t="n"/>
       <c r="AD67" s="51" t="n"/>
       <c r="AE67" s="51" t="n"/>
@@ -31867,34 +32635,78 @@
       <c r="AT67" s="51" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="51" t="n"/>
-      <c r="B68" s="51" t="n"/>
-      <c r="C68" s="51" t="n"/>
-      <c r="D68" s="51" t="n"/>
-      <c r="E68" s="51" t="n"/>
-      <c r="F68" s="51" t="n"/>
-      <c r="G68" s="51" t="n"/>
-      <c r="H68" s="51" t="n"/>
-      <c r="I68" s="51" t="n"/>
-      <c r="J68" s="51" t="n"/>
-      <c r="K68" s="51" t="n"/>
-      <c r="L68" s="51" t="n"/>
-      <c r="M68" s="51" t="n"/>
-      <c r="N68" s="51" t="n"/>
-      <c r="O68" s="51" t="n"/>
-      <c r="P68" s="51" t="n"/>
-      <c r="Q68" s="51" t="n"/>
-      <c r="R68" s="51" t="n"/>
-      <c r="S68" s="51" t="n"/>
-      <c r="T68" s="51" t="n"/>
-      <c r="U68" s="51" t="n"/>
-      <c r="V68" s="51" t="n"/>
-      <c r="W68" s="51" t="n"/>
-      <c r="X68" s="51" t="n"/>
-      <c r="Y68" s="51" t="n"/>
-      <c r="Z68" s="51" t="n"/>
-      <c r="AA68" s="51" t="n"/>
-      <c r="AB68" s="51" t="n"/>
+      <c r="A68" s="53" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B68" s="54" t="inlineStr">
+        <is>
+          <t>田一禾</t>
+        </is>
+      </c>
+      <c r="C68" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D68" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E68" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F68" s="55">
+        <f>G68+H68+I68</f>
+        <v/>
+      </c>
+      <c r="G68" s="55">
+        <f>Q68+R68</f>
+        <v/>
+      </c>
+      <c r="H68" s="55">
+        <f>U68-V68</f>
+        <v/>
+      </c>
+      <c r="I68" s="55">
+        <f>AB68</f>
+        <v/>
+      </c>
+      <c r="J68" s="55" t="n">
+        <v>232142</v>
+      </c>
+      <c r="K68" s="55" t="n">
+        <v>427600.6</v>
+      </c>
+      <c r="L68" s="55" t="n">
+        <v>9017</v>
+      </c>
+      <c r="M68" s="55" t="n">
+        <v>418583.6</v>
+      </c>
+      <c r="N68" s="56" t="n">
+        <v>1.80313601157912</v>
+      </c>
+      <c r="O68" s="55" t="n"/>
+      <c r="P68" s="56" t="n"/>
+      <c r="Q68" s="55" t="n">
+        <v>20929.18</v>
+      </c>
+      <c r="R68" s="55" t="n"/>
+      <c r="S68" s="55" t="n"/>
+      <c r="T68" s="56" t="n"/>
+      <c r="U68" s="55" t="n"/>
+      <c r="V68" s="55" t="n"/>
+      <c r="W68" s="55" t="n"/>
+      <c r="X68" s="55" t="n"/>
+      <c r="Y68" s="55" t="n"/>
+      <c r="Z68" s="55" t="n"/>
+      <c r="AA68" s="56" t="n"/>
+      <c r="AB68" s="55" t="n">
+        <v>0</v>
+      </c>
       <c r="AC68" s="51" t="n"/>
       <c r="AD68" s="51" t="n"/>
       <c r="AE68" s="51" t="n"/>
@@ -31915,34 +32727,78 @@
       <c r="AT68" s="51" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="51" t="n"/>
-      <c r="B69" s="51" t="n"/>
-      <c r="C69" s="51" t="n"/>
-      <c r="D69" s="51" t="n"/>
-      <c r="E69" s="51" t="n"/>
-      <c r="F69" s="51" t="n"/>
-      <c r="G69" s="51" t="n"/>
-      <c r="H69" s="51" t="n"/>
-      <c r="I69" s="51" t="n"/>
-      <c r="J69" s="51" t="n"/>
-      <c r="K69" s="51" t="n"/>
-      <c r="L69" s="51" t="n"/>
-      <c r="M69" s="51" t="n"/>
-      <c r="N69" s="51" t="n"/>
-      <c r="O69" s="51" t="n"/>
-      <c r="P69" s="51" t="n"/>
-      <c r="Q69" s="51" t="n"/>
-      <c r="R69" s="51" t="n"/>
-      <c r="S69" s="51" t="n"/>
-      <c r="T69" s="51" t="n"/>
-      <c r="U69" s="51" t="n"/>
-      <c r="V69" s="51" t="n"/>
-      <c r="W69" s="51" t="n"/>
-      <c r="X69" s="51" t="n"/>
-      <c r="Y69" s="51" t="n"/>
-      <c r="Z69" s="51" t="n"/>
-      <c r="AA69" s="51" t="n"/>
-      <c r="AB69" s="51" t="n"/>
+      <c r="A69" s="53" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B69" s="54" t="inlineStr">
+        <is>
+          <t>黄智超</t>
+        </is>
+      </c>
+      <c r="C69" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D69" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E69" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F69" s="55">
+        <f>G69+H69+I69</f>
+        <v/>
+      </c>
+      <c r="G69" s="55">
+        <f>Q69+R69</f>
+        <v/>
+      </c>
+      <c r="H69" s="55">
+        <f>U69-V69</f>
+        <v/>
+      </c>
+      <c r="I69" s="55">
+        <f>AB69</f>
+        <v/>
+      </c>
+      <c r="J69" s="55" t="n">
+        <v>232142</v>
+      </c>
+      <c r="K69" s="55" t="n">
+        <v>280758.1</v>
+      </c>
+      <c r="L69" s="55" t="n">
+        <v>15620</v>
+      </c>
+      <c r="M69" s="55" t="n">
+        <v>265138.1</v>
+      </c>
+      <c r="N69" s="56" t="n">
+        <v>1.14213757096949</v>
+      </c>
+      <c r="O69" s="55" t="n"/>
+      <c r="P69" s="56" t="n"/>
+      <c r="Q69" s="55" t="n">
+        <v>7993.423</v>
+      </c>
+      <c r="R69" s="55" t="n"/>
+      <c r="S69" s="55" t="n"/>
+      <c r="T69" s="56" t="n"/>
+      <c r="U69" s="55" t="n"/>
+      <c r="V69" s="55" t="n"/>
+      <c r="W69" s="55" t="n"/>
+      <c r="X69" s="55" t="n"/>
+      <c r="Y69" s="55" t="n"/>
+      <c r="Z69" s="55" t="n"/>
+      <c r="AA69" s="56" t="n"/>
+      <c r="AB69" s="55" t="n">
+        <v>1661</v>
+      </c>
       <c r="AC69" s="51" t="n"/>
       <c r="AD69" s="51" t="n"/>
       <c r="AE69" s="51" t="n"/>
@@ -31963,34 +32819,78 @@
       <c r="AT69" s="51" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="51" t="n"/>
-      <c r="B70" s="51" t="n"/>
-      <c r="C70" s="51" t="n"/>
-      <c r="D70" s="51" t="n"/>
-      <c r="E70" s="51" t="n"/>
-      <c r="F70" s="51" t="n"/>
-      <c r="G70" s="51" t="n"/>
-      <c r="H70" s="51" t="n"/>
-      <c r="I70" s="51" t="n"/>
-      <c r="J70" s="51" t="n"/>
-      <c r="K70" s="51" t="n"/>
-      <c r="L70" s="51" t="n"/>
-      <c r="M70" s="51" t="n"/>
-      <c r="N70" s="51" t="n"/>
-      <c r="O70" s="51" t="n"/>
-      <c r="P70" s="51" t="n"/>
-      <c r="Q70" s="51" t="n"/>
-      <c r="R70" s="51" t="n"/>
-      <c r="S70" s="51" t="n"/>
-      <c r="T70" s="51" t="n"/>
-      <c r="U70" s="51" t="n"/>
-      <c r="V70" s="51" t="n"/>
-      <c r="W70" s="51" t="n"/>
-      <c r="X70" s="51" t="n"/>
-      <c r="Y70" s="51" t="n"/>
-      <c r="Z70" s="51" t="n"/>
-      <c r="AA70" s="51" t="n"/>
-      <c r="AB70" s="51" t="n"/>
+      <c r="A70" s="53" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B70" s="54" t="inlineStr">
+        <is>
+          <t>徐振东</t>
+        </is>
+      </c>
+      <c r="C70" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D70" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E70" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F70" s="55">
+        <f>G70+H70+I70</f>
+        <v/>
+      </c>
+      <c r="G70" s="55">
+        <f>Q70+R70</f>
+        <v/>
+      </c>
+      <c r="H70" s="55">
+        <f>U70-V70</f>
+        <v/>
+      </c>
+      <c r="I70" s="55">
+        <f>AB70</f>
+        <v/>
+      </c>
+      <c r="J70" s="55" t="n">
+        <v>116076</v>
+      </c>
+      <c r="K70" s="55" t="n">
+        <v>40820</v>
+      </c>
+      <c r="L70" s="55" t="n">
+        <v>3924.4</v>
+      </c>
+      <c r="M70" s="55" t="n">
+        <v>36895.6</v>
+      </c>
+      <c r="N70" s="56" t="n">
+        <v>0.317857265929219</v>
+      </c>
+      <c r="O70" s="55" t="n"/>
+      <c r="P70" s="56" t="n"/>
+      <c r="Q70" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="55" t="n"/>
+      <c r="S70" s="55" t="n"/>
+      <c r="T70" s="56" t="n"/>
+      <c r="U70" s="55" t="n"/>
+      <c r="V70" s="55" t="n"/>
+      <c r="W70" s="55" t="n"/>
+      <c r="X70" s="55" t="n"/>
+      <c r="Y70" s="55" t="n"/>
+      <c r="Z70" s="55" t="n"/>
+      <c r="AA70" s="56" t="n"/>
+      <c r="AB70" s="55" t="n">
+        <v>2000</v>
+      </c>
       <c r="AC70" s="51" t="n"/>
       <c r="AD70" s="51" t="n"/>
       <c r="AE70" s="51" t="n"/>
@@ -32011,34 +32911,78 @@
       <c r="AT70" s="51" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="51" t="n"/>
-      <c r="B71" s="51" t="n"/>
-      <c r="C71" s="51" t="n"/>
-      <c r="D71" s="51" t="n"/>
-      <c r="E71" s="51" t="n"/>
-      <c r="F71" s="51" t="n"/>
-      <c r="G71" s="51" t="n"/>
-      <c r="H71" s="51" t="n"/>
-      <c r="I71" s="51" t="n"/>
-      <c r="J71" s="51" t="n"/>
-      <c r="K71" s="51" t="n"/>
-      <c r="L71" s="51" t="n"/>
-      <c r="M71" s="51" t="n"/>
-      <c r="N71" s="51" t="n"/>
-      <c r="O71" s="51" t="n"/>
-      <c r="P71" s="51" t="n"/>
-      <c r="Q71" s="51" t="n"/>
-      <c r="R71" s="51" t="n"/>
-      <c r="S71" s="51" t="n"/>
-      <c r="T71" s="51" t="n"/>
-      <c r="U71" s="51" t="n"/>
-      <c r="V71" s="51" t="n"/>
-      <c r="W71" s="51" t="n"/>
-      <c r="X71" s="51" t="n"/>
-      <c r="Y71" s="51" t="n"/>
-      <c r="Z71" s="51" t="n"/>
-      <c r="AA71" s="51" t="n"/>
-      <c r="AB71" s="51" t="n"/>
+      <c r="A71" s="53" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B71" s="54" t="inlineStr">
+        <is>
+          <t>刘晓娟</t>
+        </is>
+      </c>
+      <c r="C71" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D71" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E71" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F71" s="55">
+        <f>G71+H71+I71</f>
+        <v/>
+      </c>
+      <c r="G71" s="55">
+        <f>Q71+R71</f>
+        <v/>
+      </c>
+      <c r="H71" s="55">
+        <f>U71-V71</f>
+        <v/>
+      </c>
+      <c r="I71" s="55">
+        <f>AB71</f>
+        <v/>
+      </c>
+      <c r="J71" s="55" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K71" s="55" t="n">
+        <v>383772.2</v>
+      </c>
+      <c r="L71" s="55" t="n">
+        <v>42614</v>
+      </c>
+      <c r="M71" s="55" t="n">
+        <v>341158.2</v>
+      </c>
+      <c r="N71" s="56" t="n">
+        <v>0.8528955</v>
+      </c>
+      <c r="O71" s="55" t="n"/>
+      <c r="P71" s="56" t="n"/>
+      <c r="Q71" s="55" t="n">
+        <v>6131.44</v>
+      </c>
+      <c r="R71" s="55" t="n"/>
+      <c r="S71" s="55" t="n"/>
+      <c r="T71" s="56" t="n"/>
+      <c r="U71" s="55" t="n"/>
+      <c r="V71" s="55" t="n"/>
+      <c r="W71" s="55" t="n"/>
+      <c r="X71" s="55" t="n"/>
+      <c r="Y71" s="55" t="n"/>
+      <c r="Z71" s="55" t="n"/>
+      <c r="AA71" s="56" t="n"/>
+      <c r="AB71" s="55" t="n">
+        <v>2000</v>
+      </c>
       <c r="AC71" s="51" t="n"/>
       <c r="AD71" s="51" t="n"/>
       <c r="AE71" s="51" t="n"/>
@@ -32059,34 +33003,78 @@
       <c r="AT71" s="51" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="51" t="n"/>
-      <c r="B72" s="51" t="n"/>
-      <c r="C72" s="51" t="n"/>
-      <c r="D72" s="51" t="n"/>
-      <c r="E72" s="51" t="n"/>
-      <c r="F72" s="51" t="n"/>
-      <c r="G72" s="51" t="n"/>
-      <c r="H72" s="51" t="n"/>
-      <c r="I72" s="51" t="n"/>
-      <c r="J72" s="51" t="n"/>
-      <c r="K72" s="51" t="n"/>
-      <c r="L72" s="51" t="n"/>
-      <c r="M72" s="51" t="n"/>
-      <c r="N72" s="51" t="n"/>
-      <c r="O72" s="51" t="n"/>
-      <c r="P72" s="51" t="n"/>
-      <c r="Q72" s="51" t="n"/>
-      <c r="R72" s="51" t="n"/>
-      <c r="S72" s="51" t="n"/>
-      <c r="T72" s="51" t="n"/>
-      <c r="U72" s="51" t="n"/>
-      <c r="V72" s="51" t="n"/>
-      <c r="W72" s="51" t="n"/>
-      <c r="X72" s="51" t="n"/>
-      <c r="Y72" s="51" t="n"/>
-      <c r="Z72" s="51" t="n"/>
-      <c r="AA72" s="51" t="n"/>
-      <c r="AB72" s="51" t="n"/>
+      <c r="A72" s="53" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B72" s="54" t="inlineStr">
+        <is>
+          <t>房国超</t>
+        </is>
+      </c>
+      <c r="C72" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D72" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E72" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F72" s="55">
+        <f>G72+H72+I72</f>
+        <v/>
+      </c>
+      <c r="G72" s="55">
+        <f>Q72+R72</f>
+        <v/>
+      </c>
+      <c r="H72" s="55">
+        <f>U72-V72</f>
+        <v/>
+      </c>
+      <c r="I72" s="55">
+        <f>AB72</f>
+        <v/>
+      </c>
+      <c r="J72" s="55" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K72" s="55" t="n">
+        <v>116674</v>
+      </c>
+      <c r="L72" s="55" t="n">
+        <v>6300</v>
+      </c>
+      <c r="M72" s="55" t="n">
+        <v>110374</v>
+      </c>
+      <c r="N72" s="56" t="n">
+        <v>0.275935</v>
+      </c>
+      <c r="O72" s="55" t="n"/>
+      <c r="P72" s="56" t="n"/>
+      <c r="Q72" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="55" t="n"/>
+      <c r="S72" s="55" t="n"/>
+      <c r="T72" s="56" t="n"/>
+      <c r="U72" s="55" t="n"/>
+      <c r="V72" s="55" t="n"/>
+      <c r="W72" s="55" t="n"/>
+      <c r="X72" s="55" t="n"/>
+      <c r="Y72" s="55" t="n"/>
+      <c r="Z72" s="55" t="n"/>
+      <c r="AA72" s="56" t="n"/>
+      <c r="AB72" s="55" t="n">
+        <v>0</v>
+      </c>
       <c r="AC72" s="51" t="n"/>
       <c r="AD72" s="51" t="n"/>
       <c r="AE72" s="51" t="n"/>
@@ -32107,34 +33095,78 @@
       <c r="AT72" s="51" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="51" t="n"/>
-      <c r="B73" s="51" t="n"/>
-      <c r="C73" s="51" t="n"/>
-      <c r="D73" s="51" t="n"/>
-      <c r="E73" s="51" t="n"/>
-      <c r="F73" s="51" t="n"/>
-      <c r="G73" s="51" t="n"/>
-      <c r="H73" s="51" t="n"/>
-      <c r="I73" s="51" t="n"/>
-      <c r="J73" s="51" t="n"/>
-      <c r="K73" s="51" t="n"/>
-      <c r="L73" s="51" t="n"/>
-      <c r="M73" s="51" t="n"/>
-      <c r="N73" s="51" t="n"/>
-      <c r="O73" s="51" t="n"/>
-      <c r="P73" s="51" t="n"/>
-      <c r="Q73" s="51" t="n"/>
-      <c r="R73" s="51" t="n"/>
-      <c r="S73" s="51" t="n"/>
-      <c r="T73" s="51" t="n"/>
-      <c r="U73" s="51" t="n"/>
-      <c r="V73" s="51" t="n"/>
-      <c r="W73" s="51" t="n"/>
-      <c r="X73" s="51" t="n"/>
-      <c r="Y73" s="51" t="n"/>
-      <c r="Z73" s="51" t="n"/>
-      <c r="AA73" s="51" t="n"/>
-      <c r="AB73" s="51" t="n"/>
+      <c r="A73" s="53" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B73" s="54" t="inlineStr">
+        <is>
+          <t>王磊</t>
+        </is>
+      </c>
+      <c r="C73" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D73" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E73" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F73" s="55">
+        <f>G73+H73+I73</f>
+        <v/>
+      </c>
+      <c r="G73" s="55">
+        <f>Q73+R73</f>
+        <v/>
+      </c>
+      <c r="H73" s="55">
+        <f>U73-V73</f>
+        <v/>
+      </c>
+      <c r="I73" s="55">
+        <f>AB73</f>
+        <v/>
+      </c>
+      <c r="J73" s="55" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K73" s="55" t="n">
+        <v>146020</v>
+      </c>
+      <c r="L73" s="55" t="n">
+        <v>4465</v>
+      </c>
+      <c r="M73" s="55" t="n">
+        <v>141555</v>
+      </c>
+      <c r="N73" s="56" t="n">
+        <v>0.3538875</v>
+      </c>
+      <c r="O73" s="55" t="n"/>
+      <c r="P73" s="56" t="n"/>
+      <c r="Q73" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="55" t="n"/>
+      <c r="S73" s="55" t="n"/>
+      <c r="T73" s="56" t="n"/>
+      <c r="U73" s="55" t="n"/>
+      <c r="V73" s="55" t="n"/>
+      <c r="W73" s="55" t="n"/>
+      <c r="X73" s="55" t="n"/>
+      <c r="Y73" s="55" t="n"/>
+      <c r="Z73" s="55" t="n"/>
+      <c r="AA73" s="56" t="n"/>
+      <c r="AB73" s="55" t="n">
+        <v>0</v>
+      </c>
       <c r="AC73" s="51" t="n"/>
       <c r="AD73" s="51" t="n"/>
       <c r="AE73" s="51" t="n"/>
@@ -32155,34 +33187,78 @@
       <c r="AT73" s="51" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="51" t="n"/>
-      <c r="B74" s="51" t="n"/>
-      <c r="C74" s="51" t="n"/>
-      <c r="D74" s="51" t="n"/>
-      <c r="E74" s="51" t="n"/>
-      <c r="F74" s="51" t="n"/>
-      <c r="G74" s="51" t="n"/>
-      <c r="H74" s="51" t="n"/>
-      <c r="I74" s="51" t="n"/>
-      <c r="J74" s="51" t="n"/>
-      <c r="K74" s="51" t="n"/>
-      <c r="L74" s="51" t="n"/>
-      <c r="M74" s="51" t="n"/>
-      <c r="N74" s="51" t="n"/>
-      <c r="O74" s="51" t="n"/>
-      <c r="P74" s="51" t="n"/>
-      <c r="Q74" s="51" t="n"/>
-      <c r="R74" s="51" t="n"/>
-      <c r="S74" s="51" t="n"/>
-      <c r="T74" s="51" t="n"/>
-      <c r="U74" s="51" t="n"/>
-      <c r="V74" s="51" t="n"/>
-      <c r="W74" s="51" t="n"/>
-      <c r="X74" s="51" t="n"/>
-      <c r="Y74" s="51" t="n"/>
-      <c r="Z74" s="51" t="n"/>
-      <c r="AA74" s="51" t="n"/>
-      <c r="AB74" s="51" t="n"/>
+      <c r="A74" s="53" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B74" s="54" t="inlineStr">
+        <is>
+          <t>田一禾</t>
+        </is>
+      </c>
+      <c r="C74" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D74" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E74" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F74" s="55">
+        <f>G74+H74+I74</f>
+        <v/>
+      </c>
+      <c r="G74" s="55">
+        <f>Q74+R74</f>
+        <v/>
+      </c>
+      <c r="H74" s="55">
+        <f>U74-V74</f>
+        <v/>
+      </c>
+      <c r="I74" s="55">
+        <f>AB74</f>
+        <v/>
+      </c>
+      <c r="J74" s="55" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K74" s="55" t="n">
+        <v>442620</v>
+      </c>
+      <c r="L74" s="55" t="n">
+        <v>31350.1</v>
+      </c>
+      <c r="M74" s="55" t="n">
+        <v>411269.9</v>
+      </c>
+      <c r="N74" s="56" t="n">
+        <v>1.02817475</v>
+      </c>
+      <c r="O74" s="55" t="n"/>
+      <c r="P74" s="56" t="n"/>
+      <c r="Q74" s="55" t="n">
+        <v>12341.077</v>
+      </c>
+      <c r="R74" s="55" t="n"/>
+      <c r="S74" s="55" t="n"/>
+      <c r="T74" s="56" t="n"/>
+      <c r="U74" s="55" t="n"/>
+      <c r="V74" s="55" t="n"/>
+      <c r="W74" s="55" t="n"/>
+      <c r="X74" s="55" t="n"/>
+      <c r="Y74" s="55" t="n"/>
+      <c r="Z74" s="55" t="n"/>
+      <c r="AA74" s="56" t="n"/>
+      <c r="AB74" s="55" t="n">
+        <v>0</v>
+      </c>
       <c r="AC74" s="51" t="n"/>
       <c r="AD74" s="51" t="n"/>
       <c r="AE74" s="51" t="n"/>
@@ -32203,34 +33279,78 @@
       <c r="AT74" s="51" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="51" t="n"/>
-      <c r="B75" s="51" t="n"/>
-      <c r="C75" s="51" t="n"/>
-      <c r="D75" s="51" t="n"/>
-      <c r="E75" s="51" t="n"/>
-      <c r="F75" s="51" t="n"/>
-      <c r="G75" s="51" t="n"/>
-      <c r="H75" s="51" t="n"/>
-      <c r="I75" s="51" t="n"/>
-      <c r="J75" s="51" t="n"/>
-      <c r="K75" s="51" t="n"/>
-      <c r="L75" s="51" t="n"/>
-      <c r="M75" s="51" t="n"/>
-      <c r="N75" s="51" t="n"/>
-      <c r="O75" s="51" t="n"/>
-      <c r="P75" s="51" t="n"/>
-      <c r="Q75" s="51" t="n"/>
-      <c r="R75" s="51" t="n"/>
-      <c r="S75" s="51" t="n"/>
-      <c r="T75" s="51" t="n"/>
-      <c r="U75" s="51" t="n"/>
-      <c r="V75" s="51" t="n"/>
-      <c r="W75" s="51" t="n"/>
-      <c r="X75" s="51" t="n"/>
-      <c r="Y75" s="51" t="n"/>
-      <c r="Z75" s="51" t="n"/>
-      <c r="AA75" s="51" t="n"/>
-      <c r="AB75" s="51" t="n"/>
+      <c r="A75" s="53" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B75" s="54" t="inlineStr">
+        <is>
+          <t>黄智超</t>
+        </is>
+      </c>
+      <c r="C75" s="54" t="inlineStr">
+        <is>
+          <t>四六级</t>
+        </is>
+      </c>
+      <c r="D75" s="54" t="inlineStr">
+        <is>
+          <t>四六级项目部</t>
+        </is>
+      </c>
+      <c r="E75" s="54" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F75" s="55">
+        <f>G75+H75+I75</f>
+        <v/>
+      </c>
+      <c r="G75" s="55">
+        <f>Q75+R75</f>
+        <v/>
+      </c>
+      <c r="H75" s="55">
+        <f>U75-V75</f>
+        <v/>
+      </c>
+      <c r="I75" s="55">
+        <f>AB75</f>
+        <v/>
+      </c>
+      <c r="J75" s="55" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K75" s="55" t="n">
+        <v>425912</v>
+      </c>
+      <c r="L75" s="55" t="n">
+        <v>75357.39999999999</v>
+      </c>
+      <c r="M75" s="55" t="n">
+        <v>350554.6</v>
+      </c>
+      <c r="N75" s="56" t="n">
+        <v>0.8763865</v>
+      </c>
+      <c r="O75" s="55" t="n"/>
+      <c r="P75" s="56" t="n"/>
+      <c r="Q75" s="55" t="n">
+        <v>6306.4008</v>
+      </c>
+      <c r="R75" s="55" t="n"/>
+      <c r="S75" s="55" t="n"/>
+      <c r="T75" s="56" t="n"/>
+      <c r="U75" s="55" t="n"/>
+      <c r="V75" s="55" t="n"/>
+      <c r="W75" s="55" t="n"/>
+      <c r="X75" s="55" t="n"/>
+      <c r="Y75" s="55" t="n"/>
+      <c r="Z75" s="55" t="n"/>
+      <c r="AA75" s="56" t="n"/>
+      <c r="AB75" s="55" t="n">
+        <v>1520</v>
+      </c>
       <c r="AC75" s="51" t="n"/>
       <c r="AD75" s="51" t="n"/>
       <c r="AE75" s="51" t="n"/>
